--- a/assets/files/tcs-financial-model.xlsx
+++ b/assets/files/tcs-financial-model.xlsx
@@ -14,7 +14,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ratios" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Peer Comps" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Cover'!$A$1:$F$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Assumptions'!$A$1:$J$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Historical'!$A$1:$J$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Forecast'!$A$1:$H$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'DCF'!$A$1:$H$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Ratios'!$A$1:$J$14</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Peer Comps'!$A$1:$G$37</definedName>
+  </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
 </file>
@@ -414,7 +422,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="160">
+  <cellXfs count="163">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -607,6 +615,9 @@
     <xf numFmtId="3" fontId="26" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="26" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="20" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -865,7 +876,7 @@
   <sheetPr>
     <tabColor rgb="FF1A237E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
@@ -934,7 +945,6 @@
       <c r="E6" s="96" t="n"/>
       <c r="F6" s="96" t="n"/>
     </row>
-    <row r="7"/>
     <row r="8" ht="15" customHeight="1">
       <c r="B8" s="97" t="inlineStr">
         <is>
@@ -942,7 +952,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="98" t="inlineStr">
         <is>
@@ -1032,8 +1041,6 @@
         <v/>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19"/>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" s="98" t="inlineStr">
         <is>
@@ -1088,8 +1095,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28"/>
     <row r="29" ht="15" customHeight="1">
       <c r="B29" s="97" t="inlineStr">
         <is>
@@ -1098,8 +1103,8 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
@@ -1108,7 +1113,7 @@
   <sheetPr>
     <tabColor rgb="FF1A237E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
@@ -1188,11 +1193,11 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="112" t="inlineStr">
         <is>
-          <t>Current share price (₹, 11-Jun-2026)</t>
+          <t>Current share price (₹, 18-Jul-2026)</t>
         </is>
       </c>
       <c r="B5" s="113" t="n">
-        <v>2199</v>
+        <v>2190</v>
       </c>
       <c r="C5" s="24" t="n"/>
       <c r="D5" s="24" t="n"/>
@@ -1549,8 +1554,8 @@
       <c r="F28" s="24" t="n"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
@@ -1559,7 +1564,7 @@
   <sheetPr>
     <tabColor rgb="FF1A237E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
@@ -2881,8 +2886,8 @@
       <c r="J42" s="96" t="n"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
@@ -2891,7 +2896,7 @@
   <sheetPr>
     <tabColor rgb="FF1A237E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
@@ -3334,8 +3339,8 @@
       <c r="H16" s="102" t="n"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
@@ -3344,7 +3349,7 @@
   <sheetPr>
     <tabColor rgb="FF1A237E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
@@ -3914,8 +3919,8 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
@@ -3924,7 +3929,7 @@
   <sheetPr>
     <tabColor rgb="FF1A237E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
@@ -4431,8 +4436,8 @@
       <c r="J14" s="96" t="n"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
@@ -4441,9 +4446,9 @@
   <sheetPr>
     <tabColor rgb="FF1A237E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -4535,10 +4540,10 @@
         </is>
       </c>
       <c r="B5" s="113" t="n">
-        <v>2199</v>
+        <v>2190</v>
       </c>
       <c r="C5" s="113" t="n">
-        <v>136.01</v>
+        <v>134</v>
       </c>
       <c r="D5" s="113" t="n">
         <v>296</v>
@@ -4679,7 +4684,6 @@
       <c r="F11" s="117" t="n"/>
       <c r="G11" s="117" t="n"/>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="153" t="inlineStr">
         <is>
@@ -4726,11 +4730,10 @@
         <v/>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="153" t="inlineStr">
         <is>
-          <t>VALUATION TRIANGULATION — FOOTBALL FIELD</t>
+          <t>VALUATION TRIANGULATION — FOOTBALL FIELD (multi-method)</t>
         </is>
       </c>
       <c r="B18" s="90" t="n"/>
@@ -4765,7 +4768,7 @@
     <row r="20">
       <c r="A20" s="131" t="inlineStr">
         <is>
-          <t>DCF (intrinsic)</t>
+          <t>DCF (FCFF, intrinsic)</t>
         </is>
       </c>
       <c r="B20" s="156">
@@ -4784,7 +4787,7 @@
     <row r="21">
       <c r="A21" s="112" t="inlineStr">
         <is>
-          <t>Comparable companies</t>
+          <t>Comparable companies — P/E</t>
         </is>
       </c>
       <c r="B21" s="148">
@@ -4803,42 +4806,149 @@
     <row r="22">
       <c r="A22" s="118" t="inlineStr">
         <is>
-          <t>Blended target (70% intrinsic / 30% comps)</t>
-        </is>
+          <t>EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="B22" s="160">
+        <f>B33*0.9</f>
+        <v/>
       </c>
       <c r="C22" s="157">
-        <f>0.7*DCF!B18+0.3*B16</f>
+        <f>B33</f>
+        <v/>
+      </c>
+      <c r="D22" s="160">
+        <f>B33*1.1</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="112" t="inlineStr">
         <is>
-          <t>Current market price (₹)</t>
+          <t>Blended target (70% DCF / 30% relative)</t>
         </is>
       </c>
       <c r="C23" s="148">
-        <f>B5</f>
+        <f>0.7*DCF!B18+0.3*AVERAGE(B16,B33)</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="118" t="inlineStr">
         <is>
+          <t>Current market price (₹)</t>
+        </is>
+      </c>
+      <c r="C24" s="158">
+        <f>B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>Implied upside / (downside)</t>
         </is>
       </c>
-      <c r="C24" s="158">
-        <f>C22/B5-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25"/>
+      <c r="C25" s="161">
+        <f>C23/B5-1</f>
+        <v/>
+      </c>
+    </row>
     <row r="26">
       <c r="A26" s="159" t="inlineStr">
         <is>
-          <t>Peer multiples researched as of Jun 2026 (Kotak price to be verified). Refresh peer inputs before publication.</t>
-        </is>
+          <t>Peer prices as of Jun 2026 (IT sector fell further in Jul; refresh before publication). TCS live 18-Jul-2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="153" t="inlineStr">
+        <is>
+          <t>MARKET MULTIPLE — EV/EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="118" t="inlineStr">
+        <is>
+          <t>FY26 EBITDA (₹ Cr)</t>
+        </is>
+      </c>
+      <c r="B29" s="148" t="n">
+        <v>72900</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="118" t="inlineStr">
+        <is>
+          <t>Justified EV/EBITDA (x) — below ~16x history, above ~11x current</t>
+        </is>
+      </c>
+      <c r="B30" s="154" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="118" t="inlineStr">
+        <is>
+          <t>Enterprise value = mult × EBITDA (₹ Cr)</t>
+        </is>
+      </c>
+      <c r="B31" s="148">
+        <f>B30*B29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="118" t="inlineStr">
+        <is>
+          <t>Add: net cash (₹ Cr)</t>
+        </is>
+      </c>
+      <c r="B32" s="148">
+        <f>-Assumptions!B8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="118" t="inlineStr">
+        <is>
+          <t>EV/EBITDA-implied value / share (₹)</t>
+        </is>
+      </c>
+      <c r="B33" s="148">
+        <f>(B31+B32)/Assumptions!B6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="153" t="inlineStr">
+        <is>
+          <t>CROSS-CHECK — FCF YIELD</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="118" t="inlineStr">
+        <is>
+          <t>FY27E FCFF (₹ Cr)</t>
+        </is>
+      </c>
+      <c r="B36" s="148">
+        <f>Forecast!C16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="118" t="inlineStr">
+        <is>
+          <t>FCF yield = FCFF / market cap</t>
+        </is>
+      </c>
+      <c r="B37" s="162">
+        <f>B36/Assumptions!B7</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -4846,7 +4956,7 @@
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A18:G18"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>